--- a/base_history_metriques_tl_sgd_train_val.xlsx
+++ b/base_history_metriques_tl_sgd_train_val.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/725bbd4577e01318/Desktop/MASTER_IA_DIT/DEVOIR_DEEP_LEARNING/cnn-catsdogs-DrameSekou/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="11_2B59D2BFD340D90B1DC2C9F05016F8374EC3F82C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66548374-C4EB-4C43-A9CD-1364884A3A83}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="11_2B59D2BFD340D90B1DC2C9F05016F8374EC3F82C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40B6402C-CAC1-4DD7-B85A-3F23A8F9B96B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -72,15 +72,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -88,13 +94,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -401,7 +423,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.90625" bestFit="1" customWidth="1"/>
@@ -411,291 +433,293 @@
     <col min="8" max="8" width="11.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="1">
         <v>0.37529759450422401</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="1">
         <v>9.314713138383296E-2</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>0.87905555555555559</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>0.97022222222222221</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="1">
         <v>0.9740608228980322</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>0.96628216503992903</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3">
+      <c r="K2">
+        <f>MAX(E2:E11)</f>
+        <v>0.98044444444444445</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="1">
         <v>0.38088032416668199</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>8.7701637175761987E-2</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>0.87966666666666671</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>0.96711111111111114</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>0.97219730941704041</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>0.96184560780834072</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>0.01</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="1">
         <v>0.34744318113393252</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>9.1558752053313791E-2</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>0.88533333333333331</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>0.96777777777777774</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>0.97650248531405337</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>0.95874001774622897</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>0.01</v>
       </c>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5">
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="1">
         <v>0.30084197640419008</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>6.3629722351829204E-2</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>0.89216666666666666</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>0.97755555555555551</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>0.9748566387295986</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>0.98047914818101156</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>1E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A6">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="1">
         <v>0.25831976022322972</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>5.5087583228945733E-2</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>0.89711111111111108</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>0.98</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>0.97456140350877196</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>0.98580301685891747</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>1E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A7">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="1">
         <v>0.22145618520842661</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <v>5.6169401105907228E-2</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
         <v>0.9044444444444445</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>0.97911111111111115</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <v>0.97410008779631252</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>0.98447204968944102</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>1E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A8">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="1">
         <v>0.21469240662786701</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="1">
         <v>5.6424464997318062E-2</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="1">
         <v>0.90455555555555556</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>0.97911111111111115</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="1">
         <v>0.97535211267605637</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>0.98314108251996446</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>1E-4</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A9">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="1">
         <v>0.2141739801035987</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="1">
         <v>5.8281316081682841E-2</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="1">
         <v>0.90961111111111115</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="1">
         <v>0.97911111111111115</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="1">
         <v>0.97120418848167545</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>0.98757763975155277</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>1E-4</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A10">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="1">
         <v>0.2144705179433028</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="1">
         <v>5.7509399076302849E-2</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="1">
         <v>0.90777777777777779</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="1">
         <v>0.98</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="1">
         <v>0.97290209790209792</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>0.98757763975155277</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>1E-4</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="2">
         <v>0.2071933362020387</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="2">
         <v>5.5576937947008347E-2</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="2">
         <v>0.90666666666666662</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="2">
         <v>0.98044444444444445</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="2">
         <v>0.97962798937112494</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="2">
         <v>0.98136645962732916</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="2">
         <v>1.0000000000000001E-5</v>
       </c>
     </row>
